--- a/package/translations.xlsx
+++ b/package/translations.xlsx
@@ -23,486 +23,358 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">omegaplatinum.elin.bettersleep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Sleep (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Sleep (JP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Sleep (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mod.tooltip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customize sleep settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠設定をカスタマイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自定义睡眠设置</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一般</t>
-  </si>
-  <si>
-    <t xml:space="preserve">常规</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Can Sleep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「眠れるかどうか」を有効化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用“是否能睡觉”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable or disable the ability for the player character to sleep anytime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレイヤーキャラクターがいつでも眠れるようにするかどうかを有効または無効にします。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用或禁用玩家角色随时睡觉的能力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Auto Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オートセーブを有効にする </t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用自动保存 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set whether the game automatically saves during sleep events. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠イベント中にゲームが自動的に保存されるかどうかを設定します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">设置游戏在睡眠事件期间是否自动保存。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topic01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleep Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠时间</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slider01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Bindings </t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーバインド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按键绑定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase Sleep Hours Key </t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠時間を増やすキー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">增加睡眠时间的按键</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decrease Sleep Hours Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠時間を減らすキー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">减少睡眠时间的按键</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topic02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleep Power Multiplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠パワー倍率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠力量倍率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Sleep Power Multiplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠中のパワー回復倍率を有効化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用睡眠力量倍率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable or disable the sleep power multiplier.
-Set the multiplier for recovery during sleep (e.g., 2 for double recovery).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">睡眠中のパワー回復倍率を有効または無効にします。
-睡眠中の回復倍率を設定します（例</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">で回復量が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">倍）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">启用或禁用睡眠力量倍率。
-设置睡眠期间的恢复倍率（例如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">表示双倍恢复）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Only Unlearned Recipes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未習得のレシピのみを有効化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用仅未学习的配方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prioritize unlearned recipes when the player sleeps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレイヤーが眠るときに未習得のレシピを優先します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玩家在睡觉时优先选择未学习的配方。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Can Sleep During Meditate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瞑想中に眠れるようにする </t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用冥想时可睡觉 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable or disable the ability to sleep anytime during Meditate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瞑想中にいつでも睡眠できるようにするかどうかを有効または無効にします。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用或禁用在冥想时随时睡觉的能力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topic03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleep Delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠ディレイ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠延迟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Sleep Delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠ディレイを有効化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用睡眠延迟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable or disable turns delay before falling asleep.
-Set the number of turns it takes before the player character fully falls asleep.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>jp</t>
+  </si>
+  <si>
+    <t>cn</t>
+  </si>
+  <si>
+    <t>omegaplatinum.elin.bettersleep</t>
+  </si>
+  <si>
+    <t>Better Sleep (EN)</t>
+  </si>
+  <si>
+    <t>Better Sleep (JP)</t>
+  </si>
+  <si>
+    <t>Better Sleep (CN)</t>
+  </si>
+  <si>
+    <t>mod.tooltip</t>
+  </si>
+  <si>
+    <t>Customize sleep settings</t>
+  </si>
+  <si>
+    <t>睡眠設定をカスタマイズ</t>
+  </si>
+  <si>
+    <t>自定义睡眠设置</t>
+  </si>
+  <si>
+    <t>title01</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>一般</t>
+  </si>
+  <si>
+    <t>常规</t>
+  </si>
+  <si>
+    <t>toggle01</t>
+  </si>
+  <si>
+    <t>Enable Sleep Anytime Outside Rest</t>
+  </si>
+  <si>
+    <t>休憩中以外のいつでも睡眠を有効化</t>
+  </si>
+  <si>
+    <t>启用休息以外随时睡觉</t>
+  </si>
+  <si>
+    <t>tooltip01</t>
+  </si>
+  <si>
+    <t>Enable or disable the ability for the player character to sleep anytime outside Rest.
+Rest sleep is controlled separately by Enable Sleep During Rest.</t>
+  </si>
+  <si>
+    <t>休憩中以外でプレイヤーキャラクターがいつでも眠れるようにするかどうかを有効または無効にします。
+休憩中の睡眠は「休憩中の睡眠を有効化」で設定します。</t>
+  </si>
+  <si>
+    <t>启用或禁用玩家角色在休息以外随时睡觉的能力。
+休息时睡觉由“启用休息时睡觉”设置控制。</t>
+  </si>
+  <si>
+    <t>toggle02</t>
+  </si>
+  <si>
+    <t>Enable Auto Save During Sleep</t>
+  </si>
+  <si>
+    <t>睡眠中のオートセーブを有効化</t>
+  </si>
+  <si>
+    <t>启用睡眠期间自动保存</t>
+  </si>
+  <si>
+    <t>tooltip02</t>
+  </si>
+  <si>
+    <t>Set whether the game automatically saves during sleep events.</t>
+  </si>
+  <si>
+    <t>睡眠イベント中にゲームが自動的に保存されるかどうかを設定します。</t>
+  </si>
+  <si>
+    <t>设置游戏在睡眠事件期间是否自动保存。</t>
+  </si>
+  <si>
+    <t>topic01</t>
+  </si>
+  <si>
+    <t>Sleep Hours</t>
+  </si>
+  <si>
+    <t>睡眠時間</t>
+  </si>
+  <si>
+    <t>睡眠时间</t>
+  </si>
+  <si>
+    <t>slider01</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>時間</t>
+  </si>
+  <si>
+    <t>小时</t>
+  </si>
+  <si>
+    <t>title03</t>
+  </si>
+  <si>
+    <t>Key Bindings</t>
+  </si>
+  <si>
+    <t>キーバインド</t>
+  </si>
+  <si>
+    <t>按键绑定</t>
+  </si>
+  <si>
+    <t>text01</t>
+  </si>
+  <si>
+    <t>Increase Sleep Hours Key</t>
+  </si>
+  <si>
+    <t>睡眠時間を増やすキー</t>
+  </si>
+  <si>
+    <t>增加睡眠时间的按键</t>
+  </si>
+  <si>
+    <t>text02</t>
+  </si>
+  <si>
+    <t>Decrease Sleep Hours Key</t>
+  </si>
+  <si>
+    <t>睡眠時間を減らすキー</t>
+  </si>
+  <si>
+    <t>减少睡眠时间的按键</t>
+  </si>
+  <si>
+    <t>topic02</t>
+  </si>
+  <si>
+    <t>Sleep Recovery Multiplier</t>
+  </si>
+  <si>
+    <t>睡眠回復倍率</t>
+  </si>
+  <si>
+    <t>睡眠恢复倍率</t>
+  </si>
+  <si>
+    <t>toggle03</t>
+  </si>
+  <si>
+    <t>Enable Sleep Recovery Multiplier</t>
+  </si>
+  <si>
+    <t>睡眠中の回復倍率を有効化</t>
+  </si>
+  <si>
+    <t>启用睡眠恢复倍率</t>
+  </si>
+  <si>
+    <t>tooltip03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable or disable the sleep recovery multiplier.
+Set the multiplier for HP, stamina, and mana recovery during sleep. Must be a whole number from 1 to 10 (e.g., 2 for double recovery).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">睡眠中の回復倍率を有効または無効にします。
+睡眠中のHP、スタミナ、マナの回復倍率を設定します。1から10までの整数を指定してください（例: 2 で回復量が2倍）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用或禁用睡眠恢复倍率。
+设置睡眠期间HP、耐力和法力的恢复倍率。必须是 1 到 10 之间的整数（例如：2 表示双倍恢复）。</t>
+  </si>
+  <si>
+    <t>toggle04</t>
+  </si>
+  <si>
+    <t>Prioritize Unlearned Recipes</t>
+  </si>
+  <si>
+    <t>未習得のレシピを優先</t>
+  </si>
+  <si>
+    <t>优先未学习的配方</t>
+  </si>
+  <si>
+    <t>tooltip04</t>
+  </si>
+  <si>
+    <t>Prioritize unlearned recipes when the player sleeps.</t>
+  </si>
+  <si>
+    <t>プレイヤーが眠るときに未習得のレシピを優先します。</t>
+  </si>
+  <si>
+    <t>玩家在睡觉时优先选择未学习的配方。</t>
+  </si>
+  <si>
+    <t>toggle05</t>
+  </si>
+  <si>
+    <t>Enable Sleep During Rest</t>
+  </si>
+  <si>
+    <t>休憩中の睡眠を有効化</t>
+  </si>
+  <si>
+    <t>启用休息时睡觉</t>
+  </si>
+  <si>
+    <t>tooltip05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable or disable sleep from the Rest ability.
+Set to 'true' to allow Rest to trigger sleep, or 'false' to prevent sleeping while using Rest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">休憩アビリティから睡眠できるようにするかどうかを有効または無効にします。
+'true' に設定すると休憩で睡眠でき、'false' に設定すると休憩中は睡眠しなくなります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用或禁用通过休息能力睡觉。
+设置为 'true' 即允许休息触发睡觉，设置为 'false' 即在休息时不会睡觉。</t>
+  </si>
+  <si>
+    <t>topic03</t>
+  </si>
+  <si>
+    <t>Sleep Delay</t>
+  </si>
+  <si>
+    <t>睡眠ディレイ</t>
+  </si>
+  <si>
+    <t>睡眠延迟</t>
+  </si>
+  <si>
+    <t>toggle06</t>
+  </si>
+  <si>
+    <t>Enable Sleep Delay</t>
+  </si>
+  <si>
+    <t>睡眠ディレイを有効化</t>
+  </si>
+  <si>
+    <t>启用睡眠延迟</t>
+  </si>
+  <si>
+    <t>tooltip06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable or disable the turn delay before falling asleep.
+Set the number of turns it takes before the player character fully falls asleep. Must be a whole number from 1 to 15.</t>
   </si>
   <si>
     <t xml:space="preserve">プレイヤーキャラクターが完全に眠るまでのターンディレイを有効または無効にします。
-眠りに入るまでに必要なターン数を設定します。</t>
+眠りに入るまでに必要なターン数を設定します。1から15までの整数を指定してください。</t>
   </si>
   <si>
     <t xml:space="preserve">启用或禁用入睡前的回合延迟。
-设置玩家角色完全入睡所需的回合数。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slider02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turn(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターン数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回合数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable Sleep Simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠シミュレーションを有効化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启用睡眠模拟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tooltip07</t>
+设置玩家角色完全入睡所需的回合数。必须是 1 到 15 之间的整数。</t>
+  </si>
+  <si>
+    <t>slider02</t>
+  </si>
+  <si>
+    <t>Turn(s)</t>
+  </si>
+  <si>
+    <t>ターン数</t>
+  </si>
+  <si>
+    <t>回合数</t>
+  </si>
+  <si>
+    <t>toggle07</t>
+  </si>
+  <si>
+    <t>Enable Sleep Simulation</t>
+  </si>
+  <si>
+    <t>睡眠シミュレーションを有効化</t>
+  </si>
+  <si>
+    <t>启用睡眠模拟</t>
+  </si>
+  <si>
+    <t>tooltip07</t>
   </si>
   <si>
     <t xml:space="preserve">Set whether sleep advances time and runs normal sleep simulation.
 Set to 'true' to keep the normal black screen and time-passing sleep behavior, or 'false' to resolve sleep instantly without time simulation.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">睡眠時に時間を進め、通常の睡眠シミュレーションを実行するかどうかを設定します。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'true' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">に設定すると通常の暗転と時間経過を伴う睡眠になります。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'false' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">に設定すると時間シミュレーションなしで即座に睡眠が完了します。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">设置睡眠时是否推进时间并运行正常的睡眠模拟。
-设置为 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'true' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">时，保留正常的黑屏与时间流逝睡眠流程；
-设置为 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'false' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">时，不进行时间模拟而立即完成睡眠。</t>
-    </r>
+    <t xml:space="preserve">睡眠時に時間を進め、通常の睡眠シミュレーションを実行するかどうかを設定します。
+'true' に設定すると通常の暗転と時間経過を伴う睡眠になります。'false' に設定すると時間シミュレーションなしで即座に睡眠が完了します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设置睡眠时是否推进时间并运行正常的睡眠模拟。
+设置为 'true' 时，保留正常的黑屏与时间流逝睡眠流程；
+设置为 'false' 时，不进行时间模拟而立即完成睡眠。</t>
+  </si>
+  <si>
+    <t>slider03</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>倍率</t>
+  </si>
+  <si>
+    <t>dropdown01.item01</t>
+  </si>
+  <si>
+    <t>Select a key</t>
+  </si>
+  <si>
+    <t>キーを選択</t>
+  </si>
+  <si>
+    <t>选择按键</t>
+  </si>
+  <si>
+    <t>dropdown02.item01</t>
   </si>
 </sst>
 </file>
@@ -746,11 +618,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.42"/>
@@ -1124,6 +996,48 @@
         <v>103</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D20"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1133,6 +1047,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>